--- a/assets/Absensi.xlsx
+++ b/assets/Absensi.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABSEN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A96056-80BB-4BB4-8D88-AE14F6E4AD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D300D561-389E-4FC0-8C8D-E90E6279DB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{F37292F1-6F59-4E90-B5FC-8EE81FE23FFE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{F37292F1-6F59-4E90-B5FC-8EE81FE23FFE}"/>
   </bookViews>
   <sheets>
-    <sheet name="JULI" sheetId="4" r:id="rId1"/>
+    <sheet name="AGUSTUS" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">JULI!$A$1:$E$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">AGUSTUS!$A$1:$E$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
   <si>
     <t>DAFTAR HADIR KEGIATAN EKSTRAKURIKULER SMK NEGERI 21 JAKARTA</t>
   </si>
@@ -261,9 +261,6 @@
   </si>
   <si>
     <t>TAHUN PELAJARAN 2026/2027</t>
-  </si>
-  <si>
-    <t>BULAN JULI</t>
   </si>
   <si>
     <t>Andhika Rasyad Oktaviano</t>
@@ -354,12 +351,18 @@
   <si>
     <t>Fase E MPLB</t>
   </si>
+  <si>
+    <t>BULAN AGUSTUS</t>
+  </si>
+  <si>
+    <t>Muhammad Fadhil Khedira</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +446,11 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Arial MT"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Arial mt "/>
     </font>
   </fonts>
   <fills count="4">
@@ -586,7 +594,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -905,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D7B043-3FA0-4770-994F-09EC3A9D3C8F}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.1796875" style="1" customWidth="1"/>
@@ -936,7 +944,7 @@
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="24" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -1014,7 +1022,7 @@
         <v/>
       </c>
       <c r="E9" s="16">
-        <f t="shared" ref="E9:E63" si="1">IF(ISODD(ROW()-7),"",ROW()-7)</f>
+        <f t="shared" ref="E9:E64" si="1">IF(ISODD(ROW()-7),"",ROW()-7)</f>
         <v>2</v>
       </c>
     </row>
@@ -1023,7 +1031,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
@@ -1061,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>21</v>
@@ -1099,7 +1107,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>21</v>
@@ -1137,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>21</v>
@@ -1156,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>21</v>
@@ -1232,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>21</v>
@@ -1251,7 +1259,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
@@ -1327,10 +1335,10 @@
         <v>19</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>77</v>
       </c>
       <c r="D26" s="15">
         <f t="shared" si="0"/>
@@ -1384,7 +1392,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>21</v>
@@ -1403,7 +1411,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>21</v>
@@ -1422,7 +1430,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>21</v>
@@ -1517,10 +1525,10 @@
         <v>29</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D36" s="15">
         <f t="shared" si="0"/>
@@ -1535,10 +1543,10 @@
       <c r="A37" s="12">
         <v>30</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="B37" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="15" t="str">
@@ -1555,10 +1563,10 @@
         <v>31</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>14</v>
+        <v>60</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="D38" s="15">
         <f t="shared" si="0"/>
@@ -1574,10 +1582,10 @@
         <v>32</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D39" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1593,10 +1601,10 @@
         <v>33</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D40" s="15">
         <f t="shared" si="0"/>
@@ -1612,7 +1620,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>14</v>
@@ -1631,10 +1639,10 @@
         <v>35</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D42" s="15">
         <f t="shared" si="0"/>
@@ -1650,7 +1658,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>2</v>
@@ -1669,10 +1677,10 @@
         <v>37</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D44" s="15">
         <f t="shared" si="0"/>
@@ -1706,11 +1714,11 @@
       <c r="A46" s="12">
         <v>39</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>14</v>
+      <c r="B46" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="D46" s="15">
         <f t="shared" si="0"/>
@@ -1725,11 +1733,11 @@
       <c r="A47" s="12">
         <v>40</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>21</v>
+      <c r="B47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D47" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1745,7 +1753,7 @@
         <v>41</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>21</v>
@@ -1764,9 +1772,9 @@
         <v>42</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="15" t="str">
@@ -1783,9 +1791,9 @@
         <v>43</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="15">
@@ -1802,10 +1810,10 @@
         <v>44</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="16">
@@ -1818,10 +1826,10 @@
         <v>45</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>14</v>
+        <v>31</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D52" s="15">
         <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
@@ -1836,8 +1844,8 @@
       <c r="A53" s="12">
         <v>46</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>26</v>
+      <c r="B53" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>14</v>
@@ -1852,11 +1860,11 @@
       <c r="A54" s="12">
         <v>47</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>2</v>
+      <c r="B54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D54" s="15">
         <v>47</v>
@@ -1871,10 +1879,10 @@
         <v>48</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="16">
@@ -1887,10 +1895,10 @@
         <v>49</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D56" s="15">
         <v>49</v>
@@ -1905,10 +1913,10 @@
         <v>50</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="16">
@@ -1921,10 +1929,10 @@
         <v>51</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D58" s="15">
         <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
@@ -1940,9 +1948,9 @@
         <v>52</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="18"/>
@@ -1956,10 +1964,10 @@
         <v>53</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D60" s="18">
         <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
@@ -1975,10 +1983,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D61" s="18"/>
       <c r="E61" s="16">
@@ -1990,11 +1998,11 @@
       <c r="A62" s="12">
         <v>55</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>14</v>
+      <c r="B62" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D62" s="18">
         <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
@@ -2009,43 +2017,57 @@
       <c r="A63" s="12">
         <v>56</v>
       </c>
-      <c r="B63" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="26"/>
+      <c r="B63" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="18"/>
       <c r="E63" s="16">
-        <f t="shared" si="1"/>
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="2:5" ht="15.5">
-      <c r="B65" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="E65" s="25"/>
+    <row r="64" spans="1:5" ht="13.5">
+      <c r="A64" s="12">
+        <v>57</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="26">
+        <v>57</v>
+      </c>
+      <c r="E64" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="66" spans="2:5" ht="15.5">
       <c r="B66" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66" s="25"/>
+    </row>
+    <row r="67" spans="2:5" ht="15.5">
+      <c r="B67" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D67" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E66" s="6"/>
-    </row>
-    <row r="67" spans="2:5">
-      <c r="B67" s="6"/>
-      <c r="D67" s="6"/>
       <c r="E67" s="6"/>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="6"/>
@@ -2056,34 +2078,36 @@
     <row r="71" spans="2:5">
       <c r="B71" s="6"/>
     </row>
-    <row r="72" spans="2:5" ht="15.5">
-      <c r="B72" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>44</v>
-      </c>
+    <row r="72" spans="2:5">
+      <c r="B72" s="6"/>
     </row>
     <row r="73" spans="2:5" ht="15.5">
       <c r="B73" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" ht="15.5">
+      <c r="B74" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D74" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E73" s="10"/>
+      <c r="E74" s="10"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:C63">
-    <sortCondition ref="B9:B63"/>
-    <sortCondition ref="C9:C63"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:C64">
+    <sortCondition ref="B8:B64"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" errors="blank" r:id="rId1"/>

--- a/assets/Absensi.xlsx
+++ b/assets/Absensi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABSEN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nanas\AbsenITClubAdmin\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D300D561-389E-4FC0-8C8D-E90E6279DB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5C7DD9-16D5-4070-962D-5A4193D90BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{F37292F1-6F59-4E90-B5FC-8EE81FE23FFE}"/>
   </bookViews>
@@ -23,12 +23,24 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
   <si>
     <t>DAFTAR HADIR KEGIATAN EKSTRAKURIKULER SMK NEGERI 21 JAKARTA</t>
   </si>
@@ -356,6 +368,9 @@
   </si>
   <si>
     <t>Muhammad Fadhil Khedira</t>
+  </si>
+  <si>
+    <t>Tes</t>
   </si>
 </sst>
 </file>
@@ -582,6 +597,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -593,9 +611,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -913,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D7B043-3FA0-4770-994F-09EC3A9D3C8F}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.1796875" style="1" customWidth="1"/>
@@ -925,31 +940,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="7"/>
@@ -986,10 +1001,10 @@
       <c r="C7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="12">
@@ -1022,7 +1037,7 @@
         <v/>
       </c>
       <c r="E9" s="16">
-        <f t="shared" ref="E9:E64" si="1">IF(ISODD(ROW()-7),"",ROW()-7)</f>
+        <f t="shared" ref="E9:E65" si="1">IF(ISODD(ROW()-7),"",ROW()-7)</f>
         <v>2</v>
       </c>
     </row>
@@ -2038,7 +2053,7 @@
       <c r="C64" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="26">
+      <c r="D64" s="22">
         <v>57</v>
       </c>
       <c r="E64" s="16" t="str">
@@ -2046,57 +2061,73 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="2:5" ht="15.5">
-      <c r="B66" s="9" t="s">
+    <row r="65" spans="1:5" ht="13.5">
+      <c r="A65" s="12">
+        <v>58</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D65" s="22"/>
+      <c r="E65" s="16">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.5">
+      <c r="B67" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D66" s="25" t="s">
+      <c r="D67" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="25"/>
-    </row>
-    <row r="67" spans="2:5" ht="15.5">
-      <c r="B67" s="9" t="s">
+      <c r="E67" s="26"/>
+    </row>
+    <row r="68" spans="1:5" ht="15.5">
+      <c r="B68" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D68" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E67" s="6"/>
-    </row>
-    <row r="68" spans="2:5">
-      <c r="B68" s="6"/>
-      <c r="D68" s="6"/>
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="2:5">
+    <row r="69" spans="1:5">
       <c r="B69" s="6"/>
-    </row>
-    <row r="70" spans="2:5">
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+    </row>
+    <row r="70" spans="1:5">
       <c r="B70" s="6"/>
     </row>
-    <row r="71" spans="2:5">
+    <row r="71" spans="1:5">
       <c r="B71" s="6"/>
     </row>
-    <row r="72" spans="2:5">
+    <row r="72" spans="1:5">
       <c r="B72" s="6"/>
     </row>
-    <row r="73" spans="2:5" ht="15.5">
-      <c r="B73" s="9" t="s">
+    <row r="73" spans="1:5">
+      <c r="B73" s="6"/>
+    </row>
+    <row r="74" spans="1:5" ht="15.5">
+      <c r="B74" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D74" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="74" spans="2:5" ht="15.5">
-      <c r="B74" s="9" t="s">
+    <row r="75" spans="1:5" ht="15.5">
+      <c r="B75" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D75" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E74" s="10"/>
+      <c r="E75" s="10"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:C64">
@@ -2107,7 +2138,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" errors="blank" r:id="rId1"/>

--- a/assets/Absensi.xlsx
+++ b/assets/Absensi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nanas\AbsenITClubAdmin\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5C7DD9-16D5-4070-962D-5A4193D90BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C606D4F3-50D0-49FF-A413-550B5FE230E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{F37292F1-6F59-4E90-B5FC-8EE81FE23FFE}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
         <v>21</v>
       </c>
       <c r="D14" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v>7</v>
       </c>
       <c r="E14" s="16" t="str">
@@ -1603,7 +1603,7 @@
         <v>14</v>
       </c>
       <c r="D39" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v/>
       </c>
       <c r="E39" s="16">
@@ -1679,7 +1679,7 @@
         <v>2</v>
       </c>
       <c r="D43" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v/>
       </c>
       <c r="E43" s="16">
@@ -1717,7 +1717,7 @@
         <v>21</v>
       </c>
       <c r="D45" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v/>
       </c>
       <c r="E45" s="16">
@@ -1793,7 +1793,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v/>
       </c>
       <c r="E49" s="16">
